--- a/reports/utour/众信旅游_国内游调研表_测算底稿.xlsx
+++ b/reports/utour/众信旅游_国内游调研表_测算底稿.xlsx
@@ -1055,7 +1055,7 @@
         <v/>
       </c>
       <c r="H11" s="7">
-        <f>"人次"&amp;TEXT('测算底稿'!F54,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F54&gt;0.03,"增长",IF('测算底稿'!F54&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"门店向华中/华北扩张带来的新增出发地客源，被向小团、私家团和目的地参团的分流抵消，大团占比下降"</f>
+        <f>"人次"&amp;TEXT('测算底稿'!F54,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F54&gt;0.03,"增长",IF('测算底稿'!F54&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"整体：国内游收客"&amp;TEXT('测算底稿'!F40,"+0%;-0%")&amp;"（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构："&amp;"新增出发地客源被向小团、私家团和目的地参团的分流抵消，大团人次占比由约38%降至约28%"</f>
         <v/>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
         <v/>
       </c>
       <c r="H12" s="7">
-        <f>"人次"&amp;TEXT('测算底稿'!F55,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F55&gt;0.03,"增长",IF('测算底稿'!F55&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"新增门店客源偏好目的地参团；新疆、云南等“顶流”目的地热度延续"</f>
+        <f>"人次"&amp;TEXT('测算底稿'!F55,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F55&gt;0.03,"增长",IF('测算底稿'!F55&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"整体：国内游收客"&amp;TEXT('测算底稿'!F40,"+0%;-0%")&amp;"（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构："&amp;"新增门店客源偏好目的地参团；新疆、云南等“顶流”目的地热度延续"</f>
         <v/>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         <v/>
       </c>
       <c r="H13" s="7">
-        <f>"人次"&amp;TEXT('测算底稿'!F56,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F56&gt;0.03,"增长",IF('测算底稿'!F56&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"目的地参团与短线客群增加带动一日游"</f>
+        <f>"人次"&amp;TEXT('测算底稿'!F56,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F56&gt;0.03,"增长",IF('测算底稿'!F56&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"整体：国内游收客"&amp;TEXT('测算底稿'!F40,"+0%;-0%")&amp;"（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构："&amp;"目的地参团与短线客群增加带动一日游"</f>
         <v/>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
         <v/>
       </c>
       <c r="H14" s="7">
-        <f>"人次"&amp;TEXT('测算底稿'!F57,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F57&gt;0.03,"增长",IF('测算底稿'!F57&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"大团变小团趋势延续；五一喀纳斯、伊犁等小团线路供不应求"</f>
+        <f>"人次"&amp;TEXT('测算底稿'!F57,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F57&gt;0.03,"增长",IF('测算底稿'!F57&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"整体：国内游收客"&amp;TEXT('测算底稿'!F40,"+0%;-0%")&amp;"（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构："&amp;"大团变小团趋势延续；五一喀纳斯、伊犁等小团线路供不应求"</f>
         <v/>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v/>
       </c>
       <c r="H15" s="7">
-        <f>"人次"&amp;TEXT('测算底稿'!F58,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F58&gt;0.03,"增长",IF('测算底稿'!F58&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"新疆、云南、西北小车拼团成为主流形态"</f>
+        <f>"人次"&amp;TEXT('测算底稿'!F58,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F58&gt;0.03,"增长",IF('测算底稿'!F58&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"整体：国内游收客"&amp;TEXT('测算底稿'!F40,"+0%;-0%")&amp;"（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构："&amp;"新疆、云南、西北小车拼团成为主流形态"</f>
         <v/>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
         <v/>
       </c>
       <c r="H16" s="7">
-        <f>"人次"&amp;TEXT('测算底稿'!F59,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F59&gt;0.03,"增长",IF('测算底稿'!F59&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"家庭亲子出游偏好私密成团（2026暑期行业小团、私家团、定制预订占比稳步提升）"</f>
+        <f>"人次"&amp;TEXT('测算底稿'!F59,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F59&gt;0.03,"增长",IF('测算底稿'!F59&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"整体：国内游收客"&amp;TEXT('测算底稿'!F40,"+0%;-0%")&amp;"（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构："&amp;"家庭亲子出游偏好私密成团（2026暑期行业小团、私家团、定制预订占比稳步提升）"</f>
         <v/>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
         <v/>
       </c>
       <c r="H17" s="7">
-        <f>"人次"&amp;TEXT('测算底稿'!F60,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F60&gt;0.03,"增长",IF('测算底稿'!F60&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"家庭出游私密化，同上"</f>
+        <f>"人次"&amp;TEXT('测算底稿'!F60,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F60&gt;0.03,"增长",IF('测算底稿'!F60&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"整体：国内游收客"&amp;TEXT('测算底稿'!F40,"+0%;-0%")&amp;"（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构："&amp;"家庭出游私密化，目的地私家团与出发地私家团同步增长"</f>
         <v/>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         <v/>
       </c>
       <c r="H18" s="7">
-        <f>"人次"&amp;TEXT('测算底稿'!F61,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F61&gt;0.03,"增长",IF('测算底稿'!F61&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"定制需求扩张（2025年国内定制旅行市场规模超1,200亿元、同比+14%；2026暑期行业定制游预订人次同比超3倍）"</f>
+        <f>"人次"&amp;TEXT('测算底稿'!F61,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F61&gt;0.03,"增长",IF('测算底稿'!F61&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"整体：国内游收客"&amp;TEXT('测算底稿'!F40,"+0%;-0%")&amp;"（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构："&amp;"定制需求扩张（2025年国内定制旅行市场规模超1,200亿元、同比+14%；2026暑期行业定制游预订人次同比超3倍）"</f>
         <v/>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
         <v/>
       </c>
       <c r="H19" s="7">
-        <f>"人次"&amp;TEXT('测算底稿'!F62,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F62&gt;0.03,"增长",IF('测算底稿'!F62&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"定制需求扩张，基数小"</f>
+        <f>"人次"&amp;TEXT('测算底稿'!F62,"+0.0%;-0.0%;0.0%")&amp;"（"&amp;IF('测算底稿'!F62&gt;0.03,"增长",IF('测算底稿'!F62&lt;-0.03,"下降","基本持平"))&amp;"）。"&amp;"整体：国内游收客"&amp;TEXT('测算底稿'!F40,"+0%;-0%")&amp;"（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构："&amp;"定制需求扩张，基数小"</f>
         <v/>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
         <v/>
       </c>
       <c r="F54" s="29">
-        <f>E54/D54-1</f>
+        <f>(E$40*E27)/(D$40*D27)-1</f>
         <v/>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
         <v/>
       </c>
       <c r="F55" s="29">
-        <f>E55/D55-1</f>
+        <f>(E$40*E28)/(D$40*D28)-1</f>
         <v/>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="F56" s="29">
-        <f>E56/D56-1</f>
+        <f>(E$40*E29)/(D$40*D29)-1</f>
         <v/>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
         <v/>
       </c>
       <c r="F57" s="29">
-        <f>E57/D57-1</f>
+        <f>(E$40*E30)/(D$40*D30)-1</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v/>
       </c>
       <c r="F58" s="29">
-        <f>E58/D58-1</f>
+        <f>(E$40*E31)/(D$40*D31)-1</f>
         <v/>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
         <v/>
       </c>
       <c r="F59" s="29">
-        <f>E59/D59-1</f>
+        <f>(E$40*E32)/(D$40*D32)-1</f>
         <v/>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
         <v/>
       </c>
       <c r="F60" s="29">
-        <f>E60/D60-1</f>
+        <f>(E$40*E33)/(D$40*D33)-1</f>
         <v/>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
         <v/>
       </c>
       <c r="F61" s="29">
-        <f>E61/D61-1</f>
+        <f>(E$40*E34)/(D$40*D34)-1</f>
         <v/>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
         <v/>
       </c>
       <c r="F62" s="29">
-        <f>E62/D62-1</f>
+        <f>(E$40*E35)/(D$40*D35)-1</f>
         <v/>
       </c>
     </row>

--- a/reports/utour/众信旅游_国内游调研表_测算底稿.xlsx
+++ b/reports/utour/众信旅游_国内游调研表_测算底稿.xlsx
@@ -1781,20 +1781,20 @@
         </is>
       </c>
       <c r="B23" s="21" t="n">
-        <v>0.045</v>
+        <v>0.063</v>
       </c>
       <c r="C23" s="21" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>⚠ 全表量级取决于这一行。公司从未披露国内游收入或人次（批发主体优耐德/全景为出境批发商）。推法：国内游主要经零售门店与悠哉网销售，按约占零售成交额30%、批发成交额1%估算，合计约5%。2026年上调至7%：五一国内游GMV+38%而同期休闲成交额下滑。访谈拿到真实占比后只需改这一行</t>
+          <t>⚠ 全表量级取决于这一行。公司从未披露国内游收入或人次（批发主体优耐德/全景为出境批发商）。2025年取7%：按五一收客（公司预计超2万人次、国内游人次+168%）与门店数（2021年签约1,000余家）两条交叉核对取中值，对应全年约11万人次，相当于零售成交额约35%、批发成交额约2%为国内游。2024与2026年1–8月按同一比例缩放（×0.9、×1.4），保持各期增速不变：2026年五一国内游GMV+38%而同期休闲成交额下滑。访谈拿到真实占比后只需改这一行</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>较低可信。全部人次的量级取决于一个假设——国内团队游占众信休闲成交额的比例（2025年取5%、2026年1–8月取7%）。该比例公司从未披露，是全表最大的不确定来源；访谈拿到真实比例后，可据此对全表人次整体重算。</t>
+          <t>较低可信。全部人次的量级取决于一个假设——国内团队游占众信休闲成交额的比例（2025年取7%、2026年1–8月取9.8%）。该比例公司从未披露，是全表最大的不确定来源；访谈拿到真实比例后，可据此对全表人次整体重算。</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>公司未披露；按零售成交额约30%、批发约1%估算</t>
+          <t>公司未披露；按五一收客与门店数交叉核对取中值，约合零售成交额35%、批发2%</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C41" s="34" t="inlineStr">
         <is>
-          <t>五一国内游GMV+38%而同期休闲成交额下滑，占比上调</t>
+          <t>按2025年比例×1.4上调：五一国内游GMV+38%而同期休闲成交额下滑</t>
         </is>
       </c>
     </row>
